--- a/UTM_data/market_email_contacts_template.xlsx
+++ b/UTM_data/market_email_contacts_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\ali\repos\porsche\UTM_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ali.malek/repos/Intelligence-Hub/UTM_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AC45F2-FB90-46EB-A72C-6725A4AA3B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE838512-3DF1-A340-BFAB-159E42ACFD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="100">
   <si>
     <t>market_code</t>
   </si>
@@ -50,9 +50,6 @@
     <t>UK</t>
   </si>
   <si>
-    <t>Use semicolon ; to separate multiple names/emails</t>
-  </si>
-  <si>
     <t>PD</t>
   </si>
   <si>
@@ -279,13 +276,58 @@
   </si>
   <si>
     <t>PCEE</t>
+  </si>
+  <si>
+    <t>PIB</t>
+  </si>
+  <si>
+    <t>PKO</t>
+  </si>
+  <si>
+    <t>POF</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>PCL</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;irma.adamczyk@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;julian.sierra@omc.com;esteban.sanchez@omc.com;darryl.bobbie@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;gaurav.dayalani@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;georgette.gikas@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;araceli.sanchez@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;patricia.huang@omc.com</t>
+  </si>
+  <si>
+    <t>adriana.conte@omc.com;katharina.kleinke@omc.com;beth.hill@omc.com;chloe.wright@omc.com;christy.or@omc.com</t>
+  </si>
+  <si>
+    <t>01 May, EOD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,17 +340,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF111827"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF0F766E"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -323,6 +368,12 @@
       <color rgb="FF111827"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -701,7 +752,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -712,7 +763,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -743,260 +794,396 @@
         <v>8</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E18" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="C19" t="s">
         <v>71</v>
       </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="E19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>74</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>78</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>80</v>
+      <c r="E21" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{1AF6196C-9424-4890-86A4-3D4A87FFD656}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{275FD1F3-6141-4337-ADA0-B3242A99440F}"/>
@@ -1018,6 +1205,22 @@
     <hyperlink ref="D19" r:id="rId18" xr:uid="{B3BF117F-F0AE-4007-8279-7E70165EE1E5}"/>
     <hyperlink ref="D20" r:id="rId19" xr:uid="{BA0C0B4F-666E-44F4-AABC-5336423D7358}"/>
     <hyperlink ref="D21" r:id="rId20" xr:uid="{224C4F7E-3060-4C46-B2E5-8A92304D5190}"/>
+    <hyperlink ref="E2" r:id="rId21" xr:uid="{8E14A19F-976B-BC47-8912-E00CB52FB533}"/>
+    <hyperlink ref="E21" r:id="rId22" xr:uid="{0210FF9F-8715-0C4A-81E1-61608F30A45E}"/>
+    <hyperlink ref="E3" r:id="rId23" xr:uid="{60C5A6F1-CE63-E247-9AB1-BCD44BE811FD}"/>
+    <hyperlink ref="E5" r:id="rId24" xr:uid="{66CB0F27-24BC-9448-A890-F4F2911F88F8}"/>
+    <hyperlink ref="E8" r:id="rId25" xr:uid="{C7306751-B2A1-9F4C-8A2D-753FECC51F03}"/>
+    <hyperlink ref="E10" r:id="rId26" xr:uid="{6D799450-7E66-5644-ACE2-8B62A743BF0F}"/>
+    <hyperlink ref="E11" r:id="rId27" xr:uid="{C3F8382C-4091-F249-A238-783539A303B1}"/>
+    <hyperlink ref="E12" r:id="rId28" xr:uid="{D220D087-E08E-E048-9940-29461E3A433D}"/>
+    <hyperlink ref="E14" r:id="rId29" xr:uid="{395D94DD-437A-284B-831D-D02523A8011F}"/>
+    <hyperlink ref="E16" r:id="rId30" xr:uid="{5F399DE9-5F11-CA41-88B1-05FD933AD798}"/>
+    <hyperlink ref="E18" r:id="rId31" xr:uid="{BBD21212-6F70-B147-9C1C-4AA6172CCB2C}"/>
+    <hyperlink ref="E17" r:id="rId32" xr:uid="{327B35EB-49AC-F84C-AFC8-BCA055390421}"/>
+    <hyperlink ref="E20" r:id="rId33" xr:uid="{1661CA69-9411-6940-A978-2541AC6CB5E1}"/>
+    <hyperlink ref="E15" r:id="rId34" xr:uid="{A975BCC7-5AF7-5843-81A7-4572EEF889C8}"/>
+    <hyperlink ref="E13" r:id="rId35" xr:uid="{051BA4EA-5D33-C342-8DCF-0AC962C062CE}"/>
+    <hyperlink ref="E7" r:id="rId36" xr:uid="{418F66FA-353D-B84A-AFD2-CA9767B687B1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -1029,44 +1232,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
